--- a/用卷/2023.xlsx
+++ b/用卷/2023.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B039CAB-6394-4359-AC21-772AAE9C271D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB27262-2C16-4C27-8B20-AA2274FD602C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="217" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="91">
   <si>
     <t>年份</t>
   </si>
@@ -263,9 +263,6 @@
   </si>
   <si>
     <t>听力两次机会,较高分数计入总成绩,均使用PETS-2试题</t>
-  </si>
-  <si>
-    <t>语文为新高考二卷,历史、政治为新高考卷,其他科目为全国甲卷</t>
   </si>
   <si>
     <t>英语2次机会,一考考听力AB卷和笔试6月只有笔试,分别取较高成绩相加等于总成绩</t>
@@ -304,6 +301,13 @@
   </si>
   <si>
     <t>英语听力不计入总成绩,笔试按阅读和七选五每题2.5'→3',完形1'→2',语法填空1.5'→2'折算为总成绩</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>文综历史,政治部分是新高考卷,地理部分是全国甲卷</t>
+  </si>
+  <si>
+    <t>语文为新高考二卷,文综为西藏卷,其他科目为全国甲卷</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -843,7 +847,7 @@
         <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -857,7 +861,7 @@
         <v>6</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -871,7 +875,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -907,7 +911,7 @@
         <v>66</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -921,7 +925,7 @@
         <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -959,7 +963,7 @@
         <v>66</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -973,7 +977,7 @@
         <v>15</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -1019,7 +1023,7 @@
         <v>20</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -1205,10 +1209,12 @@
       <c r="B32" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D32" s="1"/>
+      <c r="C32" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
@@ -1233,7 +1239,7 @@
         <v>44</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -1271,7 +1277,7 @@
         <v>43</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
@@ -1305,7 +1311,7 @@
         <v>8</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -1316,7 +1322,7 @@
         <v>10</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -1327,7 +1333,7 @@
         <v>10</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
@@ -1338,7 +1344,7 @@
         <v>18</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
@@ -1349,7 +1355,7 @@
         <v>18</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
@@ -1360,7 +1366,7 @@
         <v>18</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
@@ -1371,7 +1377,7 @@
         <v>18</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
@@ -1382,7 +1388,7 @@
         <v>18</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="28.5" x14ac:dyDescent="0.2">
@@ -1393,7 +1399,7 @@
         <v>18</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
